--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-oral.xlsx
@@ -36,22 +36,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">口述 Triton LayerNorm 的完整数据流与边界。</t>
+          <t xml:space="preserve">请用 45–90 秒串联这一版 Triton LayerNorm：输入按 \[M,N\] 逐行归一化，w/b 跨行共享，反向用带锁的 \[G,N\] 梯度槽。说明前向统计量、dx、dw/db 以及共享槽同步怎样衔接。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：逐行前向计算 FP32 统计量并仿射变换；反向同时处理行内 dx 和跨行共享参数梯度。
-• [T#B#前向]：行内 mask 限定 N 列；中心化后的无效 lane 必须归零，mean/rstd 按行保存。
-• [T#B#输入梯度]：以 g=dy*w 为起点，扣除 mean(g) 与 x_hat*mean(g*x_hat)，体现行内耦合。
-• [T#B#参数梯度]：dw/db 先按 pid%G 在锁保护下累加到 \[G,N\]，再由第二 kernel 沿 G 归约。
-• [T#B#同步与精度]：CAS、block barrier、release/acquire 分别保证所有权、协作完成和数据交接；FP16 操作数在乘法前提升。
-[T#B,!c47f17#边界]：wrapper 条件决定 kernel 的覆盖范围；本课不以 kernel 数推断性能，跨双 GPU 拒绝路径尚未实机覆盖。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前向逐行计算归一化统计量并执行共享仿射变换；反向把行内输入梯度与跨行参数梯度分开处理，再通过分组槽合并所有行的参数贡献。
+• [T#B#前向与保存]：每行计算 FP32 的均值和标准差倒数 rstd，得到 x_hat=(x−mean)×rstd，再输出 x_hat×w+b。保存的行统计量可供反向恢复 x_hat；无效列在中心化后必须明确置零，避免污染方差归约。
+• [T#B#输入梯度]：设 g=dy×w、r=rstd，行内计算 dx=r×\[g−mean(g)−x_hat×mean(g×x_hat)\]。两个 mean 都沿 N 列计算，体现同一行各分量通过统计量产生的梯度耦合。
+• [T#B#参数梯度]：每行贡献 dw_row=dy×x_hat、db_row=dy。行号 pid 映射到 pid%G，在组锁保护下加到两个 FP32 \[G,N\] 槽；第二个 kernel 再沿 G 求和，得到最终 \[N\] 的 dw/db。
+• [T#B#同步职责]：CAS 决定谁持有组锁；解锁前的 block barrier 让持有者内部的协作线程汇合；release/acquire 再把完整槽更新交给下一位持有者。这三个保证不能互相代替。
+[T#B,!c47f17#边界]：这是 practice revision 2 的共享分组设计。即使 G=M、每行独占一个槽，也仍要合并行贡献；FP16 padding 即使尝试填入 mean，也应保证进入 FP32 方差归约的无效贡献严格为零。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">逐行统计量与 padding mask；dx 的两项行均值修正；dw/db 的 \[G,N\] 两阶段归约；锁协议三层职责；FP16 提升时机与 wrapper 边界</t>
+          <t xml:space="preserve">定义逐行 mean/rstd、x_hat 与中心化后的 padding 处理；写出 dx 的两项行均值修正并说明行内耦合；写出 dw/db 的行贡献及 \[G,N\] 到 \[N\] 的归约；区分 CAS、block barrier 和 release/acquire 的职责；说明 G=M 仍需归约及 FP16 padding 的精度边界</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-05-layer-norm-oral.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-05-layer-norm-oral.xlsx
@@ -36,22 +36,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">请用 45–90 秒串联这一版 Triton LayerNorm：输入按 \[M,N\] 逐行归一化，w/b 跨行共享，反向用带锁的 \[G,N\] 梯度槽。说明前向统计量、dx、dw/db 以及共享槽同步怎样衔接。</t>
+          <t xml:space="preserve">向面试官用 60–90 秒讲你实现的 Triton LayerNorm：输入看成 \[M,N\] 逐行归一化，w、b 跨行共享，反向用带锁的 FP32 \[G,N\] 梯度槽。说明前向统计量、dx、dw/db 与共享槽同步怎样衔接。</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前向逐行计算归一化统计量并执行共享仿射变换；反向把行内输入梯度与跨行参数梯度分开处理，再通过分组槽合并所有行的参数贡献。
-• [T#B#前向与保存]：每行计算 FP32 的均值和标准差倒数 rstd，得到 x_hat=(x−mean)×rstd，再输出 x_hat×w+b。保存的行统计量可供反向恢复 x_hat；无效列在中心化后必须明确置零，避免污染方差归约。
-• [T#B#输入梯度]：设 g=dy×w、r=rstd，行内计算 dx=r×\[g−mean(g)−x_hat×mean(g×x_hat)\]。两个 mean 都沿 N 列计算，体现同一行各分量通过统计量产生的梯度耦合。
-• [T#B#参数梯度]：每行贡献 dw_row=dy×x_hat、db_row=dy。行号 pid 映射到 pid%G，在组锁保护下加到两个 FP32 \[G,N\] 槽；第二个 kernel 再沿 G 求和，得到最终 \[N\] 的 dw/db。
-• [T#B#同步职责]：CAS 决定谁持有组锁；解锁前的 block barrier 让持有者内部的协作线程汇合；release/acquire 再把完整槽更新交给下一位持有者。这三个保证不能互相代替。
-[T#B,!c47f17#边界]：这是 practice revision 2 的共享分组设计。即使 G=M、每行独占一个槽，也仍要合并行贡献；FP16 padding 即使尝试填入 mean，也应保证进入 FP32 方差归约的无效贡献严格为零。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前向逐行求统计量并做共享仿射；反向把行内的 dx 与跨行的 dw/db 分开：dx 在本行内算完，dw/db 先分组累加、再归约。
+• [T#B#前向]：每行在 FP32 中求 mean 和 rstd，x_hat=(x−mean)×rstd，输出 x_hat×w+b；尾部无效列先减均值、再置零，然后才求方差。
+• [T#B#dx]：令 g=dy×w，dx=rstd×(g−mean(g)−x_hat×mean(g×x_hat))；两个 mean 都沿本行 N 列，所以同一行的分量互相耦合。
+• [T#B#dw/db]：每行贡献 dy×x_hat 与 dy，按 pid%G 加进 dw、db 各自的 \[G,N\] 槽，第二个 kernel 再沿 G 求和得到 \[N\]；即使 G=M，这一步归约也省不掉。
+• [T#B#同步]：同组 program 用 CAS 抢锁；解锁前用 block barrier 等本 program 的线程都写完；再以 release 解锁，下一位以 acquire 获锁接手更新。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">定义逐行 mean/rstd、x_hat 与中心化后的 padding 处理；写出 dx 的两项行均值修正并说明行内耦合；写出 dw/db 的行贡献及 \[G,N\] 到 \[N\] 的归约；区分 CAS、block barrier 和 release/acquire 的职责；说明 G=M 仍需归约及 FP16 padding 的精度边界</t>
+          <t xml:space="preserve">前向：FP32 的逐行 mean/rstd 与 x_hat，中心化后把无效列置零；dx：两项行均值修正，说明行内耦合；dw/db：行贡献经 pid%G 的 \[G,N\] 槽，再沿 G 归约到 \[N\]（G=M 也要归约）；同步：CAS 抢锁、block barrier 汇合、release/acquire 交接</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
